--- a/data/trans_orig/IP16B10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B10-Edad-trans_orig.xlsx
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
